--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="53">
   <si>
     <t>_reportFile</t>
   </si>
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-11T07:38:22.630Z</t>
+    <t>2026-09-11T08:23:32.141Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -100,51 +100,6 @@
     <t>https://credera.com/en-us/europe-asia-pacific-privacy-notice</t>
   </si>
   <si>
-    <t>en-us/pegaworld-2025-forrester-roundtable.report.json</t>
-  </si>
-  <si>
-    <t>en-us/pegaworld-2025-forrester-roundtable</t>
-  </si>
-  <si>
-    <t>2026-09-11T07:38:41.626Z</t>
-  </si>
-  <si>
-    <t>PegaWorld 2025: Forrester Roundtable | Credera</t>
-  </si>
-  <si>
-    <t>https://credera.com/en-us/pegaworld-2025-forrester-roundtable</t>
-  </si>
-  <si>
-    <t>en-us/salesforce-dreamforce-2024.report.json</t>
-  </si>
-  <si>
-    <t>en-us/salesforce-dreamforce-2024</t>
-  </si>
-  <si>
-    <t>2026-09-11T07:38:46.293Z</t>
-  </si>
-  <si>
-    <t>Salesforce Dreamforce 2024 | Credera</t>
-  </si>
-  <si>
-    <t>https://credera.com/en-us/salesforce-dreamforce-2024</t>
-  </si>
-  <si>
-    <t>en-us/salesforce-world-tour-2024.report.json</t>
-  </si>
-  <si>
-    <t>en-us/salesforce-world-tour-2024</t>
-  </si>
-  <si>
-    <t>2026-09-11T07:38:50.756Z</t>
-  </si>
-  <si>
-    <t>Salesforce World Tour 2024 | Credera</t>
-  </si>
-  <si>
-    <t>https://credera.com/en-us/salesforce-world-tour-2024</t>
-  </si>
-  <si>
     <t>en-us/careers/experienced-professionals.report.json</t>
   </si>
   <si>
@@ -154,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-11T07:38:28.545Z</t>
+    <t>2026-09-11T08:23:37.826Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -172,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-11T07:38:34.446Z</t>
+    <t>2026-09-11T08:23:43.526Z</t>
   </si>
   <si>
     <t>Students | Credera</t>
@@ -603,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -722,10 +677,10 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -734,24 +689,24 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -760,47 +715,47 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -809,120 +764,42 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>47</v>
       </c>
       <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-11T08:23:32.141Z</t>
+    <t>2026-09-11T10:32:42.079Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-11T08:23:37.826Z</t>
+    <t>2026-09-11T10:32:48.434Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-11T08:23:43.526Z</t>
+    <t>2026-09-11T10:32:55.181Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-11T10:32:42.079Z</t>
+    <t>2026-09-12T15:40:18.070Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-11T10:32:48.434Z</t>
+    <t>2026-09-12T15:40:23.827Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-11T10:32:55.181Z</t>
+    <t>2026-09-12T15:40:29.580Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-12T15:40:18.070Z</t>
+    <t>2026-09-14T05:45:21.793Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-12T15:40:23.827Z</t>
+    <t>2026-09-14T05:45:27.080Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-12T15:40:29.580Z</t>
+    <t>2026-09-14T05:45:33.994Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-14T05:45:21.793Z</t>
+    <t>2026-09-14T07:38:49.275Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-14T05:45:27.080Z</t>
+    <t>2026-09-14T07:38:55.025Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-14T05:45:33.994Z</t>
+    <t>2026-09-14T07:39:01.626Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-14T07:38:49.275Z</t>
+    <t>2026-09-14T08:33:21.667Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-14T07:38:55.025Z</t>
+    <t>2026-09-14T08:33:27.628Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-14T07:39:01.626Z</t>
+    <t>2026-09-14T08:33:33.581Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-14T08:33:21.667Z</t>
+    <t>2026-09-14T16:18:08.115Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -103,13 +103,13 @@
     <t>en-us/careers/experienced-professionals.report.json</t>
   </si>
   <si>
-    <t>["columns-feature","columns-feature","hero-cta"]</t>
+    <t>["hero-home","columns-feature","columns-feature","columns-feature","cards-industry","cards-industry","hero-cta"]</t>
   </si>
   <si>
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-14T08:33:27.628Z</t>
+    <t>2026-09-14T16:18:14.381Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -121,13 +121,13 @@
     <t>en-us/careers/students.report.json</t>
   </si>
   <si>
-    <t>["columns-feature","hero-cta"]</t>
+    <t>["hero-home","columns-feature","cards-industry","hero-cta"]</t>
   </si>
   <si>
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-14T08:33:33.581Z</t>
+    <t>2026-09-14T16:18:21.189Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -103,13 +103,13 @@
     <t>en-us/careers/experienced-professionals.report.json</t>
   </si>
   <si>
-    <t>["hero-home","columns-feature","columns-feature","columns-feature","cards-industry","cards-industry","hero-cta"]</t>
+    <t>["hero-home","columns-feature","columns-feature","columns-feature","cards-industry","cards-industry","cards-testimonial","hero-cta"]</t>
   </si>
   <si>
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-14T16:18:14.381Z</t>
+    <t>2026-09-15T04:54:05.960Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -121,13 +121,13 @@
     <t>en-us/careers/students.report.json</t>
   </si>
   <si>
-    <t>["hero-home","columns-feature","cards-industry","hero-cta"]</t>
+    <t>["hero-home","columns-feature","cards-industry","cards-testimonial","hero-cta"]</t>
   </si>
   <si>
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-14T16:18:21.189Z</t>
+    <t>2026-09-15T04:54:11.428Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-15T04:54:05.960Z</t>
+    <t>2026-09-15T06:17:40.088Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-15T04:54:11.428Z</t>
+    <t>2026-09-15T06:17:45.783Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-14T16:18:08.115Z</t>
+    <t>2026-09-15T16:08:28.869Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-15T06:17:40.088Z</t>
+    <t>2026-09-15T16:07:02.547Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-15T06:17:45.783Z</t>
+    <t>2026-09-15T16:07:08.782Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-15T16:07:02.547Z</t>
+    <t>2026-09-15T20:02:25.667Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-15T16:07:08.782Z</t>
+    <t>2026-09-15T20:02:32.127Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-15T20:02:25.667Z</t>
+    <t>2026-09-15T20:56:42.640Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-15T20:02:32.127Z</t>
+    <t>2026-09-15T20:56:48.182Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-15T20:56:42.640Z</t>
+    <t>2026-09-15T21:32:41.718Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-15T20:56:48.182Z</t>
+    <t>2026-09-15T21:32:48.135Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-15T21:32:41.718Z</t>
+    <t>2026-09-15T22:00:53.014Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-15T22:00:53.014Z</t>
+    <t>2026-09-16T13:03:56.137Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -73,7 +73,7 @@
     <t>careers-overview</t>
   </si>
   <si>
-    <t>2026-09-15T16:08:28.869Z</t>
+    <t>2026-09-16T15:40:24.607Z</t>
   </si>
   <si>
     <t>Careers | Credera</t>
@@ -109,7 +109,7 @@
     <t>en-us/careers/experienced-professionals</t>
   </si>
   <si>
-    <t>2026-09-16T13:03:56.137Z</t>
+    <t>2026-09-16T15:40:31.127Z</t>
   </si>
   <si>
     <t>Experienced Professionals | Credera</t>
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-15T21:32:48.135Z</t>
+    <t>2026-09-16T15:40:37.941Z</t>
   </si>
   <si>
     <t>Students | Credera</t>

--- a/tools/importer/reports/import-careers-overview.report.xlsx
+++ b/tools/importer/reports/import-careers-overview.report.xlsx
@@ -127,7 +127,7 @@
     <t>en-us/careers/students</t>
   </si>
   <si>
-    <t>2026-09-16T15:40:37.941Z</t>
+    <t>2026-09-16T18:49:14.937Z</t>
   </si>
   <si>
     <t>Students | Credera</t>
